--- a/public/templates/Template_Import_Siswa.xlsx
+++ b/public/templates/Template_Import_Siswa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ardi\Documents\Kuliah\SEM 6\Propen\SIABSEN\FE\siabsen-app-fe\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2462CE45-6DD1-4679-9351-0508D00C3456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B621AD-E1FC-473C-A40A-2EAC7D5A1182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{806C3581-A147-4810-AAB8-A3901082D4E4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>NISN</t>
   </si>
@@ -51,28 +51,19 @@
     <t>Alamat</t>
   </si>
   <si>
-    <t>Sigma</t>
-  </si>
-  <si>
-    <t>X IPA 1</t>
-  </si>
-  <si>
-    <t>Laki-laki</t>
-  </si>
-  <si>
-    <t>Depok</t>
-  </si>
-  <si>
-    <t>Sugma</t>
-  </si>
-  <si>
-    <t>Perempuan</t>
-  </si>
-  <si>
-    <t>Jakarta</t>
-  </si>
-  <si>
-    <t>XI IPA 1</t>
+    <t>Masukkan &lt;10 Digit NISN&gt;</t>
+  </si>
+  <si>
+    <t>Masukkan &lt;Nama_Siswa&gt;</t>
+  </si>
+  <si>
+    <t>Masukkan &lt;Kelas&gt;</t>
+  </si>
+  <si>
+    <t>Masukkan &lt;Laki-laki&gt; atau &lt;Perempuan&gt;</t>
+  </si>
+  <si>
+    <t>Masukkan &lt;Alamat&gt;</t>
   </si>
 </sst>
 </file>
@@ -128,8 +119,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79143A97-7F26-4218-8F2B-F9E8A58003A7}" name="Tabel1" displayName="Tabel1" ref="A1:E3" totalsRowShown="0">
-  <autoFilter ref="A1:E3" xr:uid="{79143A97-7F26-4218-8F2B-F9E8A58003A7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79143A97-7F26-4218-8F2B-F9E8A58003A7}" name="Tabel1" displayName="Tabel1" ref="A1:E2" totalsRowShown="0">
+  <autoFilter ref="A1:E2" xr:uid="{79143A97-7F26-4218-8F2B-F9E8A58003A7}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{3405BFB6-2BBC-4937-BBCC-9584EDB0BA9A}" name="NISN"/>
     <tableColumn id="2" xr3:uid="{AF41DA73-6953-4584-906A-1A29DCD1B557}" name="Nama Lengkap"/>
@@ -438,14 +429,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2FC7AD3-96A4-4501-A71C-22BCEC3B8C54}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.26953125" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="35.26953125" customWidth="1"/>
+    <col min="5" max="5" width="22.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -466,37 +457,20 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>4444444444</v>
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>5555555555</v>
-      </c>
-      <c r="B3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
